--- a/data/viajes/Pasajeros 07-Jul-2026.xlsx
+++ b/data/viajes/Pasajeros 07-Jul-2026.xlsx
@@ -8,15 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Datos/Pasajeros/Pasajeros/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86FD133D-4315-4E6E-AFC9-B85E068E2209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{86FD133D-4315-4E6E-AFC9-B85E068E2209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2DAAF12-9A6A-4D2B-9116-BAB942A637E5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="50">
   <si>
     <t>Viajes por Contrato</t>
   </si>
@@ -163,6 +172,18 @@
   </si>
   <si>
     <t>2026/07/24</t>
+  </si>
+  <si>
+    <t>ESCOLAR MEDIA_3.0</t>
+  </si>
+  <si>
+    <t>Contrato Temporal 3° Edad EV</t>
+  </si>
+  <si>
+    <t>2026/07/25</t>
+  </si>
+  <si>
+    <t>2026/07/26</t>
   </si>
 </sst>
 </file>
@@ -198,8 +219,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -539,1567 +561,1895 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="R3" t="s">
+      <c r="T3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S3" t="s">
+      <c r="U3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T3" t="s">
+      <c r="V3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>1915</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>40504</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>538</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>6190</v>
       </c>
-      <c r="G4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="1">
         <v>23124</v>
       </c>
-      <c r="I4">
+      <c r="J4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="1">
         <v>2465</v>
       </c>
-      <c r="J4">
+      <c r="L4" s="1">
         <v>1</v>
       </c>
-      <c r="K4">
+      <c r="M4" s="1">
         <v>9</v>
       </c>
-      <c r="L4">
+      <c r="N4" s="1">
         <v>36</v>
       </c>
-      <c r="M4">
+      <c r="O4" s="1">
         <v>397</v>
       </c>
-      <c r="N4">
+      <c r="P4" s="1">
         <v>21</v>
       </c>
-      <c r="O4">
+      <c r="Q4" s="1">
         <v>57</v>
       </c>
-      <c r="P4">
+      <c r="R4" s="1">
         <v>7</v>
       </c>
-      <c r="Q4">
+      <c r="S4" s="1">
         <v>80</v>
       </c>
-      <c r="R4">
+      <c r="T4" s="1">
         <v>478</v>
       </c>
-      <c r="S4">
+      <c r="U4" s="1">
         <v>1366</v>
       </c>
-      <c r="T4">
+      <c r="V4" s="1">
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>2042</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>10</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>40476</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>508</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>6230</v>
       </c>
-      <c r="G5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1">
         <v>22060</v>
       </c>
-      <c r="I5">
+      <c r="J5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1">
         <v>2576</v>
       </c>
-      <c r="J5">
+      <c r="L5" s="1">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="M5" s="1">
         <v>9</v>
       </c>
-      <c r="L5">
+      <c r="N5" s="1">
         <v>25</v>
       </c>
-      <c r="M5">
+      <c r="O5" s="1">
         <v>352</v>
       </c>
-      <c r="N5">
+      <c r="P5" s="1">
         <v>12</v>
       </c>
-      <c r="O5">
+      <c r="Q5" s="1">
         <v>51</v>
       </c>
-      <c r="P5">
+      <c r="R5" s="1">
         <v>12</v>
       </c>
-      <c r="Q5">
+      <c r="S5" s="1">
         <v>70</v>
       </c>
-      <c r="R5">
+      <c r="T5" s="1">
         <v>466</v>
       </c>
-      <c r="S5">
+      <c r="U5" s="1">
         <v>1328</v>
       </c>
-      <c r="T5">
+      <c r="V5" s="1">
         <v>286</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>1896</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>10</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>41481</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>487</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>6134</v>
       </c>
-      <c r="G6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
         <v>22707</v>
       </c>
-      <c r="I6">
+      <c r="J6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1">
         <v>2546</v>
       </c>
-      <c r="J6">
+      <c r="L6" s="1">
         <v>1</v>
       </c>
-      <c r="K6">
+      <c r="M6" s="1">
         <v>9</v>
       </c>
-      <c r="L6">
+      <c r="N6" s="1">
         <v>23</v>
       </c>
-      <c r="M6">
+      <c r="O6" s="1">
         <v>415</v>
       </c>
-      <c r="N6">
+      <c r="P6" s="1">
         <v>18</v>
       </c>
-      <c r="O6">
+      <c r="Q6" s="1">
         <v>35</v>
       </c>
-      <c r="P6">
+      <c r="R6" s="1">
         <v>12</v>
       </c>
-      <c r="Q6">
+      <c r="S6" s="1">
         <v>73</v>
       </c>
-      <c r="R6">
+      <c r="T6" s="1">
         <v>452</v>
       </c>
-      <c r="S6">
+      <c r="U6" s="1">
         <v>1293</v>
       </c>
-      <c r="T6">
+      <c r="V6" s="1">
         <v>296</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>1403</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>21848</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>252</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>2694</v>
       </c>
-      <c r="G7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H7">
+      <c r="G7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
         <v>7468</v>
       </c>
-      <c r="I7">
+      <c r="J7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
         <v>968</v>
       </c>
-      <c r="J7" t="s">
-        <v>2</v>
-      </c>
-      <c r="K7">
+      <c r="L7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M7" s="1">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="N7" s="1">
         <v>13</v>
       </c>
-      <c r="M7">
+      <c r="O7" s="1">
         <v>217</v>
       </c>
-      <c r="N7">
+      <c r="P7" s="1">
         <v>12</v>
       </c>
-      <c r="O7">
+      <c r="Q7" s="1">
         <v>7</v>
       </c>
-      <c r="P7">
-        <v>2</v>
-      </c>
-      <c r="Q7">
+      <c r="R7" s="1">
+        <v>2</v>
+      </c>
+      <c r="S7" s="1">
         <v>11</v>
       </c>
-      <c r="R7">
+      <c r="T7" s="1">
         <v>105</v>
       </c>
-      <c r="S7">
+      <c r="U7" s="1">
         <v>344</v>
       </c>
-      <c r="T7">
+      <c r="V7" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>1274</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>17768</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>174</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>1944</v>
       </c>
-      <c r="G8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8">
+      <c r="G8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
         <v>5427</v>
       </c>
-      <c r="I8">
+      <c r="J8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K8" s="1">
         <v>687</v>
       </c>
-      <c r="J8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8">
+      <c r="L8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M8" s="1">
         <v>5</v>
       </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-      <c r="M8">
+      <c r="N8" s="1">
+        <v>2</v>
+      </c>
+      <c r="O8" s="1">
         <v>242</v>
       </c>
-      <c r="N8">
+      <c r="P8" s="1">
         <v>7</v>
       </c>
-      <c r="O8">
+      <c r="Q8" s="1">
         <v>12</v>
       </c>
-      <c r="P8">
+      <c r="R8" s="1">
         <v>4</v>
       </c>
-      <c r="Q8">
+      <c r="S8" s="1">
         <v>7</v>
       </c>
-      <c r="R8">
+      <c r="T8" s="1">
         <v>48</v>
       </c>
-      <c r="S8">
+      <c r="U8" s="1">
         <v>137</v>
       </c>
-      <c r="T8">
+      <c r="V8" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>1908</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>10</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>39908</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>552</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>6439</v>
       </c>
-      <c r="G9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9">
+      <c r="G9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1">
         <v>20465</v>
       </c>
-      <c r="I9">
+      <c r="J9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="1">
         <v>2318</v>
       </c>
-      <c r="J9" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9">
+      <c r="L9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9" s="1">
         <v>8</v>
       </c>
-      <c r="L9">
+      <c r="N9" s="1">
         <v>17</v>
       </c>
-      <c r="M9">
+      <c r="O9" s="1">
         <v>279</v>
       </c>
-      <c r="N9">
+      <c r="P9" s="1">
         <v>32</v>
       </c>
-      <c r="O9">
+      <c r="Q9" s="1">
         <v>46</v>
       </c>
-      <c r="P9">
+      <c r="R9" s="1">
         <v>14</v>
       </c>
-      <c r="Q9">
+      <c r="S9" s="1">
         <v>90</v>
       </c>
-      <c r="R9">
+      <c r="T9" s="1">
         <v>533</v>
       </c>
-      <c r="S9">
+      <c r="U9" s="1">
         <v>1483</v>
       </c>
-      <c r="T9">
+      <c r="V9" s="1">
         <v>321</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>1918</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>14</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>40921</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>544</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>6519</v>
       </c>
-      <c r="G10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10">
+      <c r="G10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1">
         <v>20136</v>
       </c>
-      <c r="I10">
+      <c r="J10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="1">
         <v>2385</v>
       </c>
-      <c r="J10" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10">
+      <c r="L10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M10" s="1">
         <v>10</v>
       </c>
-      <c r="L10">
+      <c r="N10" s="1">
         <v>15</v>
       </c>
-      <c r="M10">
+      <c r="O10" s="1">
         <v>322</v>
       </c>
-      <c r="N10">
+      <c r="P10" s="1">
         <v>31</v>
       </c>
-      <c r="O10">
+      <c r="Q10" s="1">
         <v>40</v>
       </c>
-      <c r="P10">
+      <c r="R10" s="1">
         <v>5</v>
       </c>
-      <c r="Q10">
+      <c r="S10" s="1">
         <v>80</v>
       </c>
-      <c r="R10">
+      <c r="T10" s="1">
         <v>572</v>
       </c>
-      <c r="S10">
+      <c r="U10" s="1">
         <v>1563</v>
       </c>
-      <c r="T10">
+      <c r="V10" s="1">
         <v>329</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>1899</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>41181</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>546</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>6761</v>
       </c>
-      <c r="G11" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11">
+      <c r="G11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
         <v>20597</v>
       </c>
-      <c r="I11">
+      <c r="J11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1">
         <v>2399</v>
       </c>
-      <c r="J11" t="s">
-        <v>2</v>
-      </c>
-      <c r="K11">
+      <c r="L11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M11" s="1">
         <v>8</v>
       </c>
-      <c r="L11">
+      <c r="N11" s="1">
         <v>17</v>
       </c>
-      <c r="M11">
+      <c r="O11" s="1">
         <v>254</v>
       </c>
-      <c r="N11">
+      <c r="P11" s="1">
         <v>25</v>
       </c>
-      <c r="O11">
+      <c r="Q11" s="1">
         <v>45</v>
       </c>
-      <c r="P11">
+      <c r="R11" s="1">
         <v>6</v>
       </c>
-      <c r="Q11">
+      <c r="S11" s="1">
         <v>86</v>
       </c>
-      <c r="R11">
+      <c r="T11" s="1">
         <v>611</v>
       </c>
-      <c r="S11">
+      <c r="U11" s="1">
         <v>1619</v>
       </c>
-      <c r="T11">
+      <c r="V11" s="1">
         <v>355</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>1927</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>9</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>39856</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>544</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>6563</v>
       </c>
-      <c r="G12" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12">
+      <c r="G12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1">
         <v>19663</v>
       </c>
-      <c r="I12">
+      <c r="J12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" s="1">
         <v>2361</v>
       </c>
-      <c r="J12" t="s">
-        <v>2</v>
-      </c>
-      <c r="K12">
+      <c r="L12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M12" s="1">
         <v>7</v>
       </c>
-      <c r="L12">
+      <c r="N12" s="1">
         <v>17</v>
       </c>
-      <c r="M12">
+      <c r="O12" s="1">
         <v>314</v>
       </c>
-      <c r="N12">
+      <c r="P12" s="1">
         <v>26</v>
       </c>
-      <c r="O12">
+      <c r="Q12" s="1">
         <v>40</v>
       </c>
-      <c r="P12">
+      <c r="R12" s="1">
         <v>12</v>
       </c>
-      <c r="Q12">
+      <c r="S12" s="1">
         <v>81</v>
       </c>
-      <c r="R12">
+      <c r="T12" s="1">
         <v>536</v>
       </c>
-      <c r="S12">
+      <c r="U12" s="1">
         <v>1495</v>
       </c>
-      <c r="T12">
+      <c r="V12" s="1">
         <v>313</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>2029</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>17</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>41366</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>574</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>6176</v>
       </c>
-      <c r="G13" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13">
+      <c r="G13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1">
         <v>19269</v>
       </c>
-      <c r="I13">
+      <c r="J13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K13" s="1">
         <v>2463</v>
       </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
-      <c r="K13">
+      <c r="L13" s="1">
+        <v>2</v>
+      </c>
+      <c r="M13" s="1">
         <v>6</v>
       </c>
-      <c r="L13">
+      <c r="N13" s="1">
         <v>24</v>
       </c>
-      <c r="M13">
+      <c r="O13" s="1">
         <v>227</v>
       </c>
-      <c r="N13">
+      <c r="P13" s="1">
         <v>27</v>
       </c>
-      <c r="O13">
+      <c r="Q13" s="1">
         <v>38</v>
       </c>
-      <c r="P13">
+      <c r="R13" s="1">
         <v>10</v>
       </c>
-      <c r="Q13">
+      <c r="S13" s="1">
         <v>77</v>
       </c>
-      <c r="R13">
+      <c r="T13" s="1">
         <v>509</v>
       </c>
-      <c r="S13">
+      <c r="U13" s="1">
         <v>1520</v>
       </c>
-      <c r="T13">
+      <c r="V13" s="1">
         <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>1525</v>
       </c>
-      <c r="C14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1">
         <v>25195</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>277</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>3513</v>
       </c>
-      <c r="G14" t="s">
-        <v>2</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1">
         <v>9548</v>
       </c>
-      <c r="I14">
+      <c r="J14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1">
         <v>1246</v>
       </c>
-      <c r="J14">
+      <c r="L14" s="1">
         <v>1</v>
       </c>
-      <c r="K14">
+      <c r="M14" s="1">
         <v>1</v>
       </c>
-      <c r="L14">
+      <c r="N14" s="1">
         <v>10</v>
       </c>
-      <c r="M14">
+      <c r="O14" s="1">
         <v>287</v>
       </c>
-      <c r="N14">
+      <c r="P14" s="1">
         <v>3</v>
       </c>
-      <c r="O14">
+      <c r="Q14" s="1">
         <v>21</v>
       </c>
-      <c r="P14">
+      <c r="R14" s="1">
         <v>10</v>
       </c>
-      <c r="Q14">
+      <c r="S14" s="1">
         <v>17</v>
       </c>
-      <c r="R14">
+      <c r="T14" s="1">
         <v>132</v>
       </c>
-      <c r="S14">
+      <c r="U14" s="1">
         <v>456</v>
       </c>
-      <c r="T14">
+      <c r="V14" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>1263</v>
       </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1">
         <v>14485</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>216</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>2152</v>
       </c>
-      <c r="G15" t="s">
-        <v>2</v>
-      </c>
-      <c r="H15">
+      <c r="G15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1">
         <v>5436</v>
       </c>
-      <c r="I15">
+      <c r="J15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1">
         <v>714</v>
       </c>
-      <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="K15" t="s">
-        <v>2</v>
-      </c>
-      <c r="L15">
+      <c r="L15" s="1">
+        <v>2</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N15" s="1">
         <v>12</v>
       </c>
-      <c r="M15">
+      <c r="O15" s="1">
         <v>232</v>
       </c>
-      <c r="N15">
+      <c r="P15" s="1">
         <v>3</v>
       </c>
-      <c r="O15">
+      <c r="Q15" s="1">
         <v>15</v>
       </c>
-      <c r="P15" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q15">
+      <c r="R15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S15" s="1">
         <v>4</v>
       </c>
-      <c r="R15">
+      <c r="T15" s="1">
         <v>40</v>
       </c>
-      <c r="S15">
+      <c r="U15" s="1">
         <v>160</v>
       </c>
-      <c r="T15">
+      <c r="V15" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>1995</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>13</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>33033</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>570</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>6479</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="1">
         <v>1</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>17411</v>
       </c>
-      <c r="I16">
+      <c r="J16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" s="1">
         <v>2315</v>
       </c>
-      <c r="J16" t="s">
-        <v>2</v>
-      </c>
-      <c r="K16">
+      <c r="L16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M16" s="1">
         <v>6</v>
       </c>
-      <c r="L16">
+      <c r="N16" s="1">
         <v>28</v>
       </c>
-      <c r="M16">
+      <c r="O16" s="1">
         <v>259</v>
       </c>
-      <c r="N16">
+      <c r="P16" s="1">
         <v>38</v>
       </c>
-      <c r="O16">
+      <c r="Q16" s="1">
         <v>50</v>
       </c>
-      <c r="P16">
+      <c r="R16" s="1">
         <v>10</v>
       </c>
-      <c r="Q16">
+      <c r="S16" s="1">
         <v>80</v>
       </c>
-      <c r="R16">
+      <c r="T16" s="1">
         <v>515</v>
       </c>
-      <c r="S16">
+      <c r="U16" s="1">
         <v>1527</v>
       </c>
-      <c r="T16">
+      <c r="V16" s="1">
         <v>316</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>2097</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>15</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>33313</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>579</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>6371</v>
       </c>
-      <c r="G17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H17">
+      <c r="G17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1">
         <v>16896</v>
       </c>
-      <c r="I17">
+      <c r="J17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1">
         <v>2298</v>
       </c>
-      <c r="J17" t="s">
-        <v>2</v>
-      </c>
-      <c r="K17">
+      <c r="L17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M17" s="1">
         <v>8</v>
       </c>
-      <c r="L17">
+      <c r="N17" s="1">
         <v>24</v>
       </c>
-      <c r="M17">
+      <c r="O17" s="1">
         <v>294</v>
       </c>
-      <c r="N17">
+      <c r="P17" s="1">
         <v>32</v>
       </c>
-      <c r="O17">
+      <c r="Q17" s="1">
         <v>53</v>
       </c>
-      <c r="P17">
+      <c r="R17" s="1">
         <v>8</v>
       </c>
-      <c r="Q17">
+      <c r="S17" s="1">
         <v>78</v>
       </c>
-      <c r="R17">
+      <c r="T17" s="1">
         <v>538</v>
       </c>
-      <c r="S17">
+      <c r="U17" s="1">
         <v>1620</v>
       </c>
-      <c r="T17">
+      <c r="V17" s="1">
         <v>325</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>2027</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>3</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>31013</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>462</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>5856</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="1">
         <v>4</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>15183</v>
       </c>
-      <c r="I18">
+      <c r="J18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K18" s="1">
         <v>2065</v>
       </c>
-      <c r="J18" t="s">
-        <v>2</v>
-      </c>
-      <c r="K18">
+      <c r="L18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M18" s="1">
         <v>9</v>
       </c>
-      <c r="L18">
+      <c r="N18" s="1">
         <v>27</v>
       </c>
-      <c r="M18">
+      <c r="O18" s="1">
         <v>265</v>
       </c>
-      <c r="N18">
+      <c r="P18" s="1">
         <v>20</v>
       </c>
-      <c r="O18">
+      <c r="Q18" s="1">
         <v>51</v>
       </c>
-      <c r="P18">
+      <c r="R18" s="1">
         <v>16</v>
       </c>
-      <c r="Q18">
+      <c r="S18" s="1">
         <v>72</v>
       </c>
-      <c r="R18">
+      <c r="T18" s="1">
         <v>530</v>
       </c>
-      <c r="S18">
+      <c r="U18" s="1">
         <v>1511</v>
       </c>
-      <c r="T18">
+      <c r="V18" s="1">
         <v>317</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>1186</v>
       </c>
-      <c r="C19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
         <v>5728</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>78</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>677</v>
       </c>
-      <c r="G19" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19">
+      <c r="G19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1">
         <v>1857</v>
       </c>
-      <c r="I19">
+      <c r="J19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1">
         <v>300</v>
       </c>
-      <c r="J19" t="s">
-        <v>2</v>
-      </c>
-      <c r="K19">
+      <c r="L19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M19" s="1">
         <v>1</v>
       </c>
-      <c r="L19">
+      <c r="N19" s="1">
         <v>1</v>
       </c>
-      <c r="M19">
+      <c r="O19" s="1">
         <v>140</v>
       </c>
-      <c r="N19">
+      <c r="P19" s="1">
         <v>5</v>
       </c>
-      <c r="O19">
-        <v>2</v>
-      </c>
-      <c r="P19" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
+        <v>2</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S19" s="1">
         <v>1</v>
       </c>
-      <c r="R19">
+      <c r="T19" s="1">
         <v>31</v>
       </c>
-      <c r="S19">
+      <c r="U19" s="1">
         <v>128</v>
       </c>
-      <c r="T19">
+      <c r="V19" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>1112</v>
       </c>
-      <c r="C20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1">
         <v>3095</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>55</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>495</v>
       </c>
-      <c r="G20" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20">
+      <c r="G20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="1">
         <v>550</v>
       </c>
-      <c r="I20">
+      <c r="J20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" s="1">
         <v>184</v>
       </c>
-      <c r="J20" t="s">
-        <v>2</v>
-      </c>
-      <c r="K20">
-        <v>2</v>
-      </c>
-      <c r="L20">
+      <c r="L20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M20" s="1">
+        <v>2</v>
+      </c>
+      <c r="N20" s="1">
         <v>3</v>
       </c>
-      <c r="M20">
+      <c r="O20" s="1">
         <v>133</v>
       </c>
-      <c r="N20">
+      <c r="P20" s="1">
         <v>5</v>
       </c>
-      <c r="O20">
+      <c r="Q20" s="1">
         <v>8</v>
       </c>
-      <c r="P20" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q20">
+      <c r="R20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S20" s="1">
         <v>4</v>
       </c>
-      <c r="R20">
+      <c r="T20" s="1">
         <v>66</v>
       </c>
-      <c r="S20">
+      <c r="U20" s="1">
         <v>211</v>
       </c>
-      <c r="T20">
+      <c r="V20" s="1">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>1260</v>
       </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1">
         <v>9312</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>97</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>1226</v>
       </c>
-      <c r="G21" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21">
+      <c r="G21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1">
         <v>2622</v>
       </c>
-      <c r="I21">
+      <c r="J21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K21" s="1">
         <v>388</v>
       </c>
-      <c r="J21" t="s">
-        <v>2</v>
-      </c>
-      <c r="K21">
-        <v>2</v>
-      </c>
-      <c r="L21">
+      <c r="L21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M21" s="1">
+        <v>2</v>
+      </c>
+      <c r="N21" s="1">
         <v>6</v>
       </c>
-      <c r="M21">
+      <c r="O21" s="1">
         <v>110</v>
       </c>
-      <c r="N21">
+      <c r="P21" s="1">
         <v>5</v>
       </c>
-      <c r="O21">
-        <v>2</v>
-      </c>
-      <c r="P21">
-        <v>2</v>
-      </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
+        <v>2</v>
+      </c>
+      <c r="R21" s="1">
+        <v>2</v>
+      </c>
+      <c r="S21" s="1">
         <v>3</v>
       </c>
-      <c r="R21">
+      <c r="T21" s="1">
         <v>57</v>
       </c>
-      <c r="S21">
+      <c r="U21" s="1">
         <v>210</v>
       </c>
-      <c r="T21">
+      <c r="V21" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>1134</v>
       </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22">
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1">
         <v>7598</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>115</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>1159</v>
       </c>
-      <c r="G22" t="s">
-        <v>2</v>
-      </c>
-      <c r="H22">
+      <c r="G22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1">
         <v>2855</v>
       </c>
-      <c r="I22">
+      <c r="J22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K22" s="1">
         <v>393</v>
       </c>
-      <c r="J22" t="s">
-        <v>2</v>
-      </c>
-      <c r="K22">
+      <c r="L22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M22" s="1">
         <v>1</v>
       </c>
-      <c r="L22" t="s">
-        <v>2</v>
-      </c>
-      <c r="M22">
+      <c r="N22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O22" s="1">
         <v>122</v>
       </c>
-      <c r="N22">
+      <c r="P22" s="1">
         <v>6</v>
       </c>
-      <c r="O22" t="s">
-        <v>2</v>
-      </c>
-      <c r="P22" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q22">
+      <c r="Q22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S22" s="1">
         <v>4</v>
       </c>
-      <c r="R22">
+      <c r="T22" s="1">
         <v>34</v>
       </c>
-      <c r="S22">
+      <c r="U22" s="1">
         <v>115</v>
       </c>
-      <c r="T22">
+      <c r="V22" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>1670</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>8</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>17800</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>287</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>3555</v>
       </c>
-      <c r="G23" t="s">
-        <v>2</v>
-      </c>
-      <c r="H23">
+      <c r="G23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="1">
         <v>5924</v>
       </c>
-      <c r="I23">
+      <c r="J23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
         <v>951</v>
       </c>
-      <c r="J23" t="s">
-        <v>2</v>
-      </c>
-      <c r="K23">
+      <c r="L23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M23" s="1">
         <v>4</v>
       </c>
-      <c r="L23">
+      <c r="N23" s="1">
         <v>12</v>
       </c>
-      <c r="M23">
+      <c r="O23" s="1">
         <v>166</v>
       </c>
-      <c r="N23">
+      <c r="P23" s="1">
         <v>15</v>
       </c>
-      <c r="O23">
+      <c r="Q23" s="1">
         <v>25</v>
       </c>
-      <c r="P23">
+      <c r="R23" s="1">
         <v>5</v>
       </c>
-      <c r="Q23">
+      <c r="S23" s="1">
         <v>37</v>
       </c>
-      <c r="R23">
+      <c r="T23" s="1">
         <v>306</v>
       </c>
-      <c r="S23">
+      <c r="U23" s="1">
         <v>982</v>
       </c>
-      <c r="T23">
+      <c r="V23" s="1">
         <v>211</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>1612</v>
       </c>
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24">
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1">
         <v>17911</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>226</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>2696</v>
       </c>
-      <c r="G24" t="s">
-        <v>2</v>
-      </c>
-      <c r="H24">
+      <c r="G24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="1">
         <v>3970</v>
       </c>
-      <c r="I24">
+      <c r="J24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1">
         <v>876</v>
       </c>
-      <c r="J24">
+      <c r="L24" s="1">
         <v>1</v>
       </c>
-      <c r="K24">
+      <c r="M24" s="1">
         <v>4</v>
       </c>
-      <c r="L24">
+      <c r="N24" s="1">
         <v>10</v>
       </c>
-      <c r="M24">
+      <c r="O24" s="1">
         <v>145</v>
       </c>
-      <c r="N24">
+      <c r="P24" s="1">
         <v>14</v>
       </c>
-      <c r="O24">
+      <c r="Q24" s="1">
         <v>29</v>
       </c>
-      <c r="P24">
+      <c r="R24" s="1">
         <v>6</v>
       </c>
-      <c r="Q24">
+      <c r="S24" s="1">
         <v>55</v>
       </c>
-      <c r="R24">
+      <c r="T24" s="1">
         <v>305</v>
       </c>
-      <c r="S24">
+      <c r="U24" s="1">
         <v>1030</v>
       </c>
-      <c r="T24">
+      <c r="V24" s="1">
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>1888</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>5</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>31132</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>482</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>5546</v>
       </c>
-      <c r="G25" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25">
+      <c r="G25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="1">
         <v>9623</v>
       </c>
-      <c r="I25">
+      <c r="J25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
         <v>1564</v>
       </c>
-      <c r="J25" t="s">
-        <v>2</v>
-      </c>
-      <c r="K25">
+      <c r="L25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M25" s="1">
         <v>6</v>
       </c>
-      <c r="L25">
+      <c r="N25" s="1">
         <v>22</v>
       </c>
-      <c r="M25">
+      <c r="O25" s="1">
         <v>177</v>
       </c>
-      <c r="N25">
+      <c r="P25" s="1">
         <v>29</v>
       </c>
-      <c r="O25">
+      <c r="Q25" s="1">
         <v>41</v>
       </c>
-      <c r="P25">
+      <c r="R25" s="1">
         <v>5</v>
       </c>
-      <c r="Q25">
+      <c r="S25" s="1">
         <v>79</v>
       </c>
-      <c r="R25">
+      <c r="T25" s="1">
         <v>431</v>
       </c>
-      <c r="S25">
+      <c r="U25" s="1">
         <v>1291</v>
       </c>
-      <c r="T25">
+      <c r="V25" s="1">
         <v>279</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>1840</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>14</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>32924</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>458</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>5279</v>
       </c>
-      <c r="G26" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26">
+      <c r="G26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="1">
         <v>9693</v>
       </c>
-      <c r="I26">
+      <c r="J26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1">
         <v>1865</v>
       </c>
-      <c r="J26" t="s">
-        <v>2</v>
-      </c>
-      <c r="K26">
+      <c r="L26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M26" s="1">
         <v>4</v>
       </c>
-      <c r="L26">
+      <c r="N26" s="1">
         <v>16</v>
       </c>
-      <c r="M26">
+      <c r="O26" s="1">
         <v>244</v>
       </c>
-      <c r="N26">
+      <c r="P26" s="1">
         <v>24</v>
       </c>
-      <c r="O26">
+      <c r="Q26" s="1">
         <v>41</v>
       </c>
-      <c r="P26">
+      <c r="R26" s="1">
         <v>7</v>
       </c>
-      <c r="Q26">
+      <c r="S26" s="1">
         <v>78</v>
       </c>
-      <c r="R26">
+      <c r="T26" s="1">
         <v>490</v>
       </c>
-      <c r="S26">
+      <c r="U26" s="1">
         <v>1408</v>
       </c>
-      <c r="T26">
+      <c r="V26" s="1">
         <v>299</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B27">
-        <v>583</v>
-      </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27">
-        <v>6594</v>
-      </c>
-      <c r="E27">
-        <v>151</v>
-      </c>
-      <c r="F27">
-        <v>1751</v>
-      </c>
-      <c r="G27" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27">
-        <v>2061</v>
-      </c>
-      <c r="I27">
-        <v>602</v>
-      </c>
-      <c r="J27" t="s">
-        <v>2</v>
-      </c>
-      <c r="K27">
+      <c r="B27" s="1">
+        <v>1976</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1">
+        <v>38062</v>
+      </c>
+      <c r="E27" s="1">
+        <v>466</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5827</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="1">
+        <v>12069</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>2123</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M27" s="1">
+        <v>5</v>
+      </c>
+      <c r="N27" s="1">
+        <v>28</v>
+      </c>
+      <c r="O27" s="1">
+        <v>264</v>
+      </c>
+      <c r="P27" s="1">
+        <v>23</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>37</v>
+      </c>
+      <c r="R27" s="1">
+        <v>7</v>
+      </c>
+      <c r="S27" s="1">
+        <v>70</v>
+      </c>
+      <c r="T27" s="1">
+        <v>480</v>
+      </c>
+      <c r="U27" s="1">
+        <v>1437</v>
+      </c>
+      <c r="V27" s="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1401</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1">
+        <v>23737</v>
+      </c>
+      <c r="E28" s="1">
+        <v>306</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3130</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="1">
         <v>1</v>
       </c>
-      <c r="L27">
-        <v>6</v>
-      </c>
-      <c r="M27">
-        <v>64</v>
-      </c>
-      <c r="N27">
-        <v>11</v>
-      </c>
-      <c r="O27">
-        <v>12</v>
-      </c>
-      <c r="P27">
-        <v>3</v>
-      </c>
-      <c r="Q27">
-        <v>34</v>
-      </c>
-      <c r="R27">
-        <v>223</v>
-      </c>
-      <c r="S27">
-        <v>673</v>
-      </c>
-      <c r="T27">
-        <v>139</v>
+      <c r="I28" s="1">
+        <v>7806</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1044</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
+        <v>2</v>
+      </c>
+      <c r="N28" s="1">
+        <v>14</v>
+      </c>
+      <c r="O28" s="1">
+        <v>217</v>
+      </c>
+      <c r="P28" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>29</v>
+      </c>
+      <c r="R28" s="1">
+        <v>2</v>
+      </c>
+      <c r="S28" s="1">
+        <v>18</v>
+      </c>
+      <c r="T28" s="1">
+        <v>112</v>
+      </c>
+      <c r="U28" s="1">
+        <v>417</v>
+      </c>
+      <c r="V28" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1301</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1">
+        <v>15382</v>
+      </c>
+      <c r="E29" s="1">
+        <v>171</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1985</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1">
+        <v>4809</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1</v>
+      </c>
+      <c r="K29" s="1">
+        <v>623</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M29" s="1">
+        <v>2</v>
+      </c>
+      <c r="N29" s="1">
+        <v>5</v>
+      </c>
+      <c r="O29" s="1">
+        <v>184</v>
+      </c>
+      <c r="P29" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>16</v>
+      </c>
+      <c r="R29" s="1">
+        <v>5</v>
+      </c>
+      <c r="S29" s="1">
+        <v>4</v>
+      </c>
+      <c r="T29" s="1">
+        <v>58</v>
+      </c>
+      <c r="U29" s="1">
+        <v>177</v>
+      </c>
+      <c r="V29" s="1">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
